--- a/backend/order/src/test/resources/workbooks/DS-ORDER-3X/confirmed/정식 발주 1주.xlsx
+++ b/backend/order/src/test/resources/workbooks/DS-ORDER-3X/confirmed/정식 발주 1주.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,11 +436,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>542</v>
+        <v>709</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -451,11 +451,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>647</v>
+        <v>791</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -466,11 +466,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>727</v>
+        <v>987</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -481,11 +481,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>438</v>
+        <v>27</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -496,11 +496,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>533</v>
+        <v>79</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -511,11 +511,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>642</v>
+        <v>278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -526,11 +526,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>299</v>
+        <v>50</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -541,11 +541,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>813</v>
+        <v>981</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -556,11 +556,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -571,11 +571,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>633</v>
+        <v>653</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -586,11 +586,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>806</v>
+        <v>523</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -601,11 +601,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>861</v>
+        <v>443</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -616,11 +616,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>216</v>
+        <v>421</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -631,11 +631,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>730</v>
+        <v>665</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -646,11 +646,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>312</v>
+        <v>560</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -661,11 +661,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50</v>
+        <v>166</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -676,11 +676,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>518</v>
+        <v>95</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -691,11 +691,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>714</v>
+        <v>90</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -706,11 +706,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>348</v>
+        <v>953</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>837</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -736,11 +736,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>697</v>
+        <v>559</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -751,11 +751,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>938</v>
+        <v>410</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -766,11 +766,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>865</v>
+        <v>659</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -781,11 +781,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -796,11 +796,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -811,11 +811,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>808</v>
+        <v>725</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -826,11 +826,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A6722030900</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>86</v>
+        <v>757</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -841,11 +841,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>750</v>
+        <v>69</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -856,11 +856,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>936</v>
+        <v>98</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>669</v>
+        <v>128</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>29696-2U000</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>477</v>
+        <v>636</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -901,11 +901,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>280</v>
+        <v>66</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -916,11 +916,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>61</v>
+        <v>692</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -931,11 +931,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>842</v>
+        <v>683</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -946,11 +946,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>905</v>
+        <v>189</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -961,11 +961,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>882</v>
+        <v>22</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -976,11 +976,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>378</v>
+        <v>150</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -991,11 +991,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>330</v>
+        <v>21</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1006,11 +1006,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>766</v>
+        <v>518</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1021,11 +1021,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>107</v>
+        <v>545</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1036,11 +1036,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>19</v>
+        <v>811</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1051,11 +1051,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>689</v>
+        <v>275</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1066,11 +1066,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>184</v>
+        <v>390</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1081,11 +1081,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>376</v>
+        <v>777</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1096,11 +1096,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>988</v>
+        <v>760</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1111,11 +1111,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>284</v>
+        <v>799</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1126,11 +1126,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>105</v>
+        <v>353</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1141,11 +1141,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>25450-P7200</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>844</v>
+        <v>288</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1156,11 +1156,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1171,11 +1171,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>29673-2F910</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>420</v>
+        <v>739</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1186,11 +1186,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>995</v>
+        <v>652</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1201,11 +1201,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>288</v>
+        <v>518</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1216,11 +1216,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>716</v>
+        <v>533</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1231,11 +1231,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>829</v>
+        <v>66</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1246,11 +1246,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>25451-P7200</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>674</v>
+        <v>889</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1261,11 +1261,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1276,11 +1276,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>722</v>
+        <v>171</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>28421-2M100</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>70</v>
+        <v>801</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1306,11 +1306,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>29673-2F910</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>116</v>
+        <v>925</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1321,11 +1321,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>A6722031002</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>943</v>
+        <v>700</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1336,11 +1336,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>504</v>
+        <v>128</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>704</v>
+        <v>768</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1366,11 +1366,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>A6722030900</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>195</v>
+        <v>12</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1381,11 +1381,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A6722031002</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>398</v>
+        <v>889</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1396,11 +1396,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>636</v>
+        <v>260</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>893</v>
+        <v>493</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1426,11 +1426,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>28415-08400</t>
+          <t>28422-2M100</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>911</v>
+        <v>402</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1441,11 +1441,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>28674-L5500</t>
+          <t>29673-2R060</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>923</v>
+        <v>193</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1456,11 +1456,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>29673-2R060</t>
+          <t>29673-2F900</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>504</v>
+        <v>576</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1471,11 +1471,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>25451-P7200</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>125</v>
+        <v>768</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1486,11 +1486,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>25450-P7200</t>
+          <t>28415-08400</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1501,11 +1501,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>29673-2F900</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>74</v>
+        <v>339</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1516,11 +1516,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>28421-2M100</t>
+          <t>29696-2U000</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>680</v>
+        <v>436</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1531,11 +1531,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>28422-2M100</t>
+          <t>28674-L5500</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>22</v>
+        <v>337</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1546,15 +1546,1035 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>28421-2M100</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>855</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>29673-2F910</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>595</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>28422-2M100</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>132</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>A6722030900</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>699</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>29673-2F900</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>193</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>833</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>A6722030900</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>57</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>25450-P7200</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>80</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>25451-P7200</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>896</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>28421-2M100</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>802</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>28421-2M100</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>345</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>29673-2F910</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>576</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>25451-P7200</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>18</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>28422-2M100</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>215</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>28421-2M100</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>587</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>28421-2M100</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>767</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>A6722031002</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>258</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>25451-P7200</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>387</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>A6722031002</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>515</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>760</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>A6722030900</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>788</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>164</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>29673-2F900</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>964</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>25450-P7200</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>34</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>564</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>28422-2M100</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>661</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
           <t>28674-L5500</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>899</v>
-      </c>
-      <c r="C76" t="inlineStr">
+      <c r="B102" t="n">
+        <v>908</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>29673-2F900</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>983</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>28422-2M100</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>11</v>
+      </c>
+      <c r="C104" t="inlineStr">
         <is>
           <t>2026-02-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>28415-08400</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>395</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>28674-L5500</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>754</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>28421-2M100</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>116</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>552</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>439</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>25451-P7200</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>994</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>29673-2F900</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>155</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>28674-L5500</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>296</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>29673-2F910</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>54</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>928</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>A6722030900</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>432</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>28674-L5500</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>927</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>28422-2M100</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>479</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>28674-L5500</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>96</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>A6722031002</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>107</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>A6722030900</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>146</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>28415-08400</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>849</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>25450-P7200</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>86</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>A6722031002</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>591</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>29673-2F900</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>455</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>28415-08400</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>997</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>29673-2R060</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>252</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>28421-2M100</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>277</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>28422-2M100</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>958</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>25450-P7200</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>727</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>28674-L5500</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>344</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>28422-2M100</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>473</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>28421-2M100</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>249</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>29673-2F910</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>976</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>149</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>A6722031002</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>121</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>29673-2R060</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>118</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>29673-2R060</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>470</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>25451-P7200</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>331</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>25450-P7200</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>133</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>A6722030900</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>376</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>29696-2U000</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>472</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>28421-2M100</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>484</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>28421-2M100</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>882</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>29673-2F910</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>102</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
         </is>
       </c>
     </row>
